--- a/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>application-sub-type</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Application sub type</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Further classification of the application type for specific variations within the main application type</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>submission-date</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Submission date</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>Date the application is submitted in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>modules</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Modules[]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>List of required modules for this application that can be used to validate the application</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -786,21 +786,29 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Documents[]</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -844,19 +852,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -900,19 +908,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -922,7 +930,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -956,29 +964,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1020,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Uploaded date</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1068,29 +1076,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>base64-content</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Base64</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1150,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>base64-content</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Base64</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1214,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1218,7 +1234,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1278,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>file-size</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>File size</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1306,37 +1322,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
+          <t>Fee</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>file-size</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>File size</t>
-        </is>
-      </c>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1380,19 +1388,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1436,75 +1444,67 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>transactions</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Transactions[]</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Fee</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>transactions</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Transactions[]</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,21 +1514,13 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1536,23 +1528,31 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1586,21 +1586,29 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1644,24 +1652,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1671,8 +1679,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1680,63 +1696,47 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,21 +1754,29 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1812,19 +1820,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1834,7 +1842,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1868,19 +1876,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1924,19 +1932,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1980,19 +1988,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2026,29 +2034,21 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>user-role</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>User role</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,64 +2111,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>user-role</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>User role</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2176,23 +2168,31 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>Contact details</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,21 +2226,29 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2250,7 +2258,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2284,24 +2292,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>contact-priority</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Contact priority</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2311,72 +2319,64 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
+          <t>Applicants[]</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>contact-priority</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Contact priority</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,21 +2394,29 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2452,19 +2460,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2482,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2516,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2564,19 +2572,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2628,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2642,77 +2650,61 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Conflict to declare</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2720,12 +2712,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>conflict-person-name</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Conflict person name</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2736,17 +2728,17 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2752,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2776,7 +2768,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2791,21 +2783,29 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2826,34 +2826,34 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Declaration</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>checklist</t>
+          <t>declaration</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>A name of a person</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2879,16 +2879,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2896,12 +2888,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2912,12 +2904,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2936,12 +2928,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2952,12 +2944,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2967,21 +2959,29 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>interest-details</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>applicant-interest</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Applicant interest</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,7 +2992,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Description of the applicant's interest in the land</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -3007,16 +3007,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Interest details</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>interest-details</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
@@ -3024,23 +3016,39 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
+          <t>Owner details[]</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3050,7 +3058,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3084,19 +3092,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3106,7 +3114,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3140,19 +3148,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3196,19 +3204,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3252,19 +3260,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3274,7 +3282,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3298,39 +3306,31 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>informed-of-application</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3344,41 +3344,49 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>owner-details</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
+          <t>Interested persons[]</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3412,19 +3420,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3434,7 +3442,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3468,19 +3476,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3524,19 +3532,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3580,19 +3588,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3602,7 +3610,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3626,29 +3634,21 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>nature-of-interest</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Nature of interest</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>nature-of-interest</t>
+          <t>informed-of-application</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
+          <t>Informed of application</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3696,12 +3696,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>reason-not-informed</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
+          <t>Reason not informed</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3744,79 +3744,71 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>reason-not-informed</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Reason not informed</t>
-        </is>
-      </c>
+          <t>Pre-application advice sought</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -3824,12 +3816,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3840,17 +3832,17 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3864,12 +3856,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3880,7 +3872,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3904,12 +3896,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3920,7 +3912,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -3944,12 +3936,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Advice summary</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3960,7 +3952,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -3975,37 +3967,53 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>site-boundary</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Site boundary</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -4015,16 +4023,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -4152,12 +4152,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4200,7 +4200,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4248,7 +4248,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4296,7 +4296,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4344,12 +4344,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>uprns</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>UPRNs[]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4407,64 +4407,56 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="2" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Information to help the planning authority arrange a site visit</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>uprns</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4472,12 +4464,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4488,12 +4480,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4512,12 +4504,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Contact reference</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4528,17 +4520,17 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4552,23 +4544,31 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>other-contact</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4602,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4616,7 +4616,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4664,7 +4664,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -4673,54 +4673,6 @@
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Information to help the planning authority arrange a site visit</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>other-contact</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4728,30 +4680,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A49:A63"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B69:B77"/>
-    <mergeCell ref="B45"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="A45"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B49:B63"/>
-    <mergeCell ref="B78:B83"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B36:B41"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A69:A77"/>
-    <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="A48:A62"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="A77:A82"/>
+    <mergeCell ref="A44"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="B2:B18"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B62"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="B77:B82"/>
+    <mergeCell ref="B68:B76"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A68:A76"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="B44"/>
+    <mergeCell ref="A23:A30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">

--- a/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -521,37 +521,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>submission-reference</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Submission reference</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -560,7 +560,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>A unique reference for the submission</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -579,17 +579,17 @@
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -627,27 +627,27 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>planning-authority</t>
+          <t>specification-profile</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Planning authority</t>
+          <t>Specification profile</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
+          <t>The specification profile used to determine context-specific allowed codelist values for the application</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -675,27 +675,27 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>submission-date</t>
+          <t>planning-authority</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Submission date</t>
+          <t>Planning authority</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -704,12 +704,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Date the application is submitted in YYYY-MM-DD format</t>
+          <t>A reference of the planning authority the application has been submitted to, e.g. local-authority:CMD for London borough of Camden</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -723,27 +723,27 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>modules</t>
+          <t>submitted-at</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Modules[]</t>
+          <t>Submitted at</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -752,12 +752,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>List of required modules for this application that can be used to validate the application</t>
+          <t>The date and time the application was submitted</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -771,49 +771,41 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>created-at</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Documents[]</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
+          <t>Created at</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
+          <t>The date and time the submission payload was created</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -827,17 +819,17 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -852,19 +844,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>The name or title of the document</t>
+          <t>Unique reference for the document within this application submission, generated by the submitting system</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -883,17 +875,17 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -908,19 +900,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Brief description of what the document contains</t>
+          <t>The name or title of the document</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -930,7 +922,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -939,17 +931,17 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -964,29 +956,29 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>document-types</t>
+          <t>description</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Document types[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Brief description of what the document contains</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -995,17 +987,17 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1020,24 +1012,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>uploaded-date</t>
+          <t>document-types</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Uploaded date</t>
+          <t>Document types[]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>The date the document was uploaded to the application</t>
+          <t>List of codelist references that the document covers</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1051,17 +1043,17 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1076,37 +1068,29 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>file</t>
+          <t>uploaded-date</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>base64-content</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Base64</t>
-        </is>
-      </c>
+          <t>Uploaded date</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Base64-encoded content of the file for inline file uploads</t>
+          <t>The date the document was uploaded to the application</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1099,17 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1150,17 +1134,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>filename</t>
+          <t>base64-content</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Filename</t>
+          <t>Base64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Name of the file being uploaded</t>
+          <t>Base64-encoded content of the file for inline file uploads</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1163,17 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1214,17 +1198,17 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>mime-type</t>
+          <t>filename</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>MIME type</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>The file's MIME type such as application/pdf or image/jpeg</t>
+          <t>Name of the file being uploaded</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1234,7 +1218,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1278,22 +1262,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>file-size</t>
+          <t>mime-type</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>File size</t>
+          <t>MIME type</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Size of the file in bytes that can be used to enforce limits</t>
+          <t>The file's MIME type such as application/pdf or image/jpeg</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1307,54 +1291,62 @@
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Fee</t>
+          <t>Documents[]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>file</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>file-size</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>File size</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>The total amount due for the application fee</t>
+          <t>Size of the file in bytes that can be used to enforce limits</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1355,17 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1388,24 +1380,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>amount-paid</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Amount paid</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>The amount paid towards the application fee</t>
+          <t>The total amount due for the application fee</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1419,17 +1411,17 @@
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>The details of the application payload to be submitted</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Submission details</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1444,67 +1436,75 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>transactions</t>
+          <t>amount-paid</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Transactions[]</t>
+          <t>Amount paid</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>References to payments or financial transactions related to this application</t>
+          <t>The amount paid towards the application fee</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Agent contact details</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>agent-contact</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information if an agent is being used.</t>
+          <t>Details about the submitted payload, including how it is identified, routed, validated, handled and traced</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>agent-reference</t>
+          <t>submission-details</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Agent reference</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Submission details</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>transactions</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Transactions[]</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>A reference to an agent object</t>
+          <t>References to payments or financial transactions related to this application</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1514,13 +1514,21 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Agent contact details</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>agent-contact</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1528,31 +1536,23 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>agent-reference</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Agent reference</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>A reference to an agent object</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1586,21 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1618,7 +1610,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1644,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1679,16 +1671,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Agent details</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>agent-details</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1696,47 +1680,63 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Agent details</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>agent-details</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Name and contact information if an agent is being used.</t>
@@ -1754,29 +1754,21 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -1786,7 +1778,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -1820,19 +1812,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1868,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -1932,19 +1924,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -1988,19 +1980,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2010,7 +2002,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2026,29 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2096,12 +2096,12 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2111,56 +2111,64 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2168,31 +2176,23 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2226,29 +2226,21 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2258,7 +2250,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2284,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2319,64 +2311,72 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2394,29 +2394,21 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -2426,7 +2418,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2460,19 +2452,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2482,7 +2474,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2516,19 +2508,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2572,19 +2564,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2628,19 +2620,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2650,61 +2642,77 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>Name and contact information for the parties making the application.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>applicants</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -2712,12 +2720,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>conflict-person-name</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Conflict person name</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2728,17 +2736,17 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Name of the individual with the conflict of interest that matches one of the names provided in applicants/agent section</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2760,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2768,7 +2776,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -2783,29 +2791,21 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2826,34 +2826,34 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Declaration</t>
+          <t>Checklist</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>declaration</t>
+          <t>checklist</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2864,7 +2864,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>A name of a person</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2879,8 +2879,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2888,12 +2896,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2904,12 +2912,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2928,12 +2936,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2944,12 +2952,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2959,29 +2967,21 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Interest details</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>interest-details</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,12 +2992,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Description of the applicant's interest in the land</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3007,8 +3007,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>interest-details</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
@@ -3016,49 +3024,33 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>owner-details</t>
+          <t>applicant-interest-type</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Applicant interest type</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The applicant’s relationship to the land, property or building</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3092,19 +3084,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3114,7 +3106,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3148,19 +3140,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3204,19 +3196,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3260,19 +3252,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3282,7 +3274,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3306,31 +3298,39 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3344,49 +3344,41 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>informed-of-application</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3420,19 +3412,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3442,7 +3434,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3468,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3532,19 +3524,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -3588,19 +3580,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3610,7 +3602,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3634,21 +3626,29 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>nature-of-interest</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>nature-of-interest</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
+          <t>Nature of interest</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3696,12 +3696,12 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>reason-not-informed</t>
+          <t>informed-of-application</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Reason not informed</t>
+          <t>Informed of application</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3744,71 +3744,79 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>reason-not-informed</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Reason not informed</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -3816,12 +3824,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3832,17 +3840,17 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3864,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3872,7 +3880,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3896,12 +3904,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3912,12 +3920,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -3936,12 +3944,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Advice date</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3952,12 +3960,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3967,53 +3975,37 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -4023,8 +4015,16 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="2" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>site-boundary</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Geometry of the site of the development, typically in GeoJSON format</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>wkt</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>address-text</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Address Text</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Flexible field for capturing addresses</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>postcode</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
+          <t>Postcode</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -4152,12 +4152,12 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>The postal code</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4200,12 +4200,12 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4248,12 +4248,12 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
+          <t>Latitude</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4296,12 +4296,12 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4344,12 +4344,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject. For parking changes, this describes how the proposed works affect existing car parking arrangements.</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4392,7 +4392,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>A text description providing details about the subject.</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4407,56 +4407,64 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="2" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4464,12 +4472,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4480,12 +4488,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4504,12 +4512,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site visit contact type</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4520,17 +4528,17 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4544,31 +4552,23 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4602,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Phone number</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4616,7 +4616,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The complete name of a person</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>number</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4664,15 +4664,63 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4680,30 +4728,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B35:B40"/>
-    <mergeCell ref="A48:A62"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="A77:A82"/>
-    <mergeCell ref="A44"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="B48:B62"/>
-    <mergeCell ref="B63:B67"/>
-    <mergeCell ref="B77:B82"/>
-    <mergeCell ref="B68:B76"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B30"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="A68:A76"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A35:A40"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="B44"/>
-    <mergeCell ref="A23:A30"/>
+    <mergeCell ref="A49:A63"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="A36:A41"/>
+    <mergeCell ref="B69:B77"/>
+    <mergeCell ref="B45"/>
+    <mergeCell ref="A78:A83"/>
+    <mergeCell ref="A64:A68"/>
+    <mergeCell ref="A45"/>
+    <mergeCell ref="A32:A35"/>
+    <mergeCell ref="B49:B63"/>
+    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B32:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
+++ b/generated/spreadsheet/verbose/lawful-development-certificate-ldc-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1980,19 +1980,27 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2036,19 +2044,27 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2082,21 +2098,37 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2130,12 +2162,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2144,12 +2176,12 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2159,56 +2191,64 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2216,31 +2256,23 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -2274,29 +2306,21 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -2306,7 +2330,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2340,24 +2364,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -2367,64 +2391,72 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2442,29 +2474,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -2474,7 +2498,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2508,19 +2532,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -2564,19 +2588,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2620,19 +2644,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2676,77 +2700,101 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict of interest</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>conflict-of-interest</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>conflict-to-declare</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Conflict to declare</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2755,57 +2803,89 @@
       <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>person-reference</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Person reference</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>Reference to the applicant or agent with the conflict</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>MAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
-        </is>
-      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2816,44 +2896,36 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>national-req-types</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>National requirement types[]</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2864,7 +2936,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>List of the document types required for the given application type</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2874,34 +2946,26 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2912,7 +2976,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -2922,26 +2986,34 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>national-req-types</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>National requirement types[]</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2952,12 +3024,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2967,8 +3039,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -2976,12 +3056,12 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2992,12 +3072,12 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3007,29 +3087,21 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Interest details</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>interest-details</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>applicant-interest-type</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Applicant interest type</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -3040,12 +3112,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The applicant’s relationship to the land, property or building</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -3059,60 +3131,52 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>owner-details</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Declaration date</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Interest details</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>interest-details</t>
+        </is>
+      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
@@ -3120,44 +3184,28 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>owner-details</t>
+          <t>applicant-interest-type</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Owner details[]</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>first-name</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>First Name</t>
-        </is>
-      </c>
+          <t>Applicant interest type</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The applicant’s relationship to the land, property or building</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -3196,19 +3244,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -3218,7 +3266,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3252,19 +3300,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -3308,19 +3356,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -3330,7 +3378,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3354,26 +3402,42 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Whether the owner has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -3392,12 +3456,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3412,19 +3476,27 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>contact-address</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3448,12 +3520,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3468,19 +3540,27 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>contact-address</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3490,7 +3570,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3504,44 +3584,36 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>interested-persons</t>
+          <t>owner-details</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Interested persons[]</t>
+          <t>Owner details[]</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>informed-of-application</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>last-name</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
+          <t>Informed of application</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>Whether the owner has been informed of the application</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -3580,19 +3652,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -3602,7 +3674,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3636,19 +3708,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -3658,7 +3730,7 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3682,21 +3754,29 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>nature-of-interest</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Nature of interest</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>last-name</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Description of the nature of a person's interest in the property</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -3730,26 +3810,42 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>informed-of-application</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Informed of application</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Whether the person has been informed of the application</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3778,21 +3874,37 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>reason-not-informed</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Reason not informed</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Reason why a person was not informed of the application</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -3807,50 +3919,66 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3859,28 +3987,36 @@
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>nature-of-interest</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Nature of interest</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>Description of the nature of a person's interest in the property</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3890,7 +4026,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3899,38 +4035,46 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>informed-of-application</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Informed of application</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether the person has been informed of the application</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3939,33 +4083,41 @@
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Names and contact details for all parties with an interest in the proposed develpoment.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>interested-persons</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+          <t>Interested persons[]</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>reason-not-informed</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Reason not informed</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Reason why a person was not informed of the application</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -3975,8 +4127,16 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -3984,12 +4144,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -4000,68 +4160,52 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>site-boundary</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Site boundary</t>
-        </is>
-      </c>
+          <t>Officer name</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -4075,36 +4219,28 @@
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>address-text</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Address Text</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -4123,41 +4259,33 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>postcode</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Postcode</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4171,41 +4299,33 @@
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>easting</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Easting</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -4215,8 +4335,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="n"/>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4234,12 +4362,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4248,17 +4376,17 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4282,31 +4410,39 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4330,26 +4466,34 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4378,21 +4522,29 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -4426,21 +4578,29 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -4455,50 +4615,50 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>easting</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Easting</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4507,38 +4667,46 @@
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>northing</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Northing</t>
+        </is>
+      </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4547,33 +4715,41 @@
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4587,27 +4763,27 @@
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
+          <t>Site locations[]</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>fullname</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Full name</t>
+          <t>Longitude</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4616,23 +4792,31 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="2" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -4640,36 +4824,28 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Site seen from public area</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4688,39 +4864,215 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>contact-reference</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>fullname</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Full name</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -4728,30 +5080,30 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A49:A63"/>
-    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="B73:B81"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A51:A67"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="A36:A41"/>
-    <mergeCell ref="B69:B77"/>
-    <mergeCell ref="B45"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="A45"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="B49:B63"/>
-    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="A82:A87"/>
+    <mergeCell ref="B37:B43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="B47"/>
+    <mergeCell ref="B82:B87"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="A48:A50"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B36:B41"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A73:A81"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B20:B23"/>
-    <mergeCell ref="A69:A77"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B51:B67"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
